--- a/Alalisis_Alaterio/Transformacion/Dataset_Transformado_.xlsx
+++ b/Alalisis_Alaterio/Transformacion/Dataset_Transformado_.xlsx
@@ -419,7 +419,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>nivelsatisfaccion</t>
+          <t>nivelSatisfaccion</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -434,22 +434,22 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>país_Brasil</t>
+          <t>pais_brasil</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>país_Chile</t>
+          <t>pais_chile</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>país_Ecuador</t>
+          <t>pais_ecuador</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>país_España</t>
+          <t>pais_españa</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
@@ -460,7 +460,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2" t="n">
         <v>1</v>
@@ -486,7 +486,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B3" t="n">
         <v>0</v>
@@ -538,7 +538,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B5" t="n">
         <v>0</v>
@@ -564,7 +564,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B6" t="n">
         <v>1</v>
@@ -590,7 +590,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B7" t="n">
         <v>0</v>
